--- a/mails.xlsx
+++ b/mails.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel\PycharmProjects\PythonProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel\Desktop\Python automation email\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C3A7FF-FA70-4BDA-A4CD-8B021C067DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AAC75C-7748-42F8-878B-E7575B31C22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Email</t>
   </si>
@@ -37,10 +37,13 @@
     <t>defg@gmail.com</t>
   </si>
   <si>
-    <t>defg</t>
-  </si>
-  <si>
     <t>ghij@gmail.com</t>
+  </si>
+  <si>
+    <t>def</t>
+  </si>
+  <si>
+    <t>ghij</t>
   </si>
 </sst>
 </file>
@@ -451,15 +454,15 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -467,7 +470,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{ED0FBA18-BA6D-4038-AA83-DD26BE286456}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{893D48F0-1D66-42B6-AA87-6244453A4AEA}"/>
     <hyperlink ref="A4" r:id="rId3" xr:uid="{53943019-1C03-4260-A9CD-2F039A1054F8}"/>
-    <hyperlink ref="B4" r:id="rId4" xr:uid="{D1F4F715-F0D4-41E6-978B-F2BC6F835ED0}"/>
+    <hyperlink ref="B4" r:id="rId4" display="ghij@gmail.com" xr:uid="{D1F4F715-F0D4-41E6-978B-F2BC6F835ED0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
